--- a/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_28-10-2026.xlsx
+++ b/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_28-10-2026.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
+          <t>Error: 404 Client Error: Not Found for url: https://www.insulationshop.co/powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£24.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Error: HTTPConnectionPool(host='localhost', port=64597): Read timed out. (read timeout=120)</t>
+          <t>Was:£0.00ex VAT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -862,28 +862,28 @@
   (Session info: chrome=156.0.8078.48)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff71e9e3f45]
-	(No symbol) [0x7ff71e8e4f90]
-	(No symbol) [0x7ff71ece97ad]
-	(No symbol) [0x7ff71ef73188]
-	(No symbol) [0x7ff71e7565d6]
-	(No symbol) [0x7ff71e7571b2]
-	(No symbol) [0x7ff71e763dc0]
-	(No symbol) [0x7ff71e7934f4]
-	(No symbol) [0x7ff71e789a8a]
-	(No symbol) [0x7ff71e7925d1]
-	(No symbol) [0x7ff71e777cb9]
-	(No symbol) [0x7ff71e778ff3]
-	(No symbol) [0x7ff71ee9e1a1]
-	(No symbol) [0x7ff71eec181b]
-	(No symbol) [0x7ff71eeb7ece]
-	(No symbol) [0x7ff71eb0b10e]
-	(No symbol) [0x7ff71e8f3db5]
-	(No symbol) [0x7ff71e8ee694]
-	(No symbol) [0x7ff71e8ee824]
-	(No symbol) [0x7ff71e8d6bdc]
-	(No symbol) [0x7ffa76dbdda7]
-	(No symbol) [0x7ffa784bee4c]
+	(No symbol) [0x7ff702a42e35]
+	(No symbol) [0x7ff702951dc0]
+	(No symbol) [0x7ff702d34fb1]
+	(No symbol) [0x7ff702fab158]
+	(No symbol) [0x7ff7027c6686]
+	(No symbol) [0x7ff7027c7262]
+	(No symbol) [0x7ff7027d3e80]
+	(No symbol) [0x7ff702807194]
+	(No symbol) [0x7ff7027fdc6a]
+	(No symbol) [0x7ff702806271]
+	(No symbol) [0x7ff7027ebae9]
+	(No symbol) [0x7ff7027ece13]
+	(No symbol) [0x7ff702ed63c1]
+	(No symbol) [0x7ff702ef987b]
+	(No symbol) [0x7ff702eee240]
+	(No symbol) [0x7ff702b6b4ee]
+	(No symbol) [0x7ff702960985]
+	(No symbol) [0x7ff70295b9e4]
+	(No symbol) [0x7ff70295bb74]
+	(No symbol) [0x7ff702944bfc]
+	(No symbol) [0x7ff944fedda7]
+	(No symbol) [0x7ff945c5ee4c]
 </t>
         </is>
       </c>
@@ -1813,28 +1813,28 @@
   (Session info: chrome=156.0.8078.48)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff71e9e3f45]
-	(No symbol) [0x7ff71e8e4f90]
-	(No symbol) [0x7ff71ece97ad]
-	(No symbol) [0x7ff71ef73188]
-	(No symbol) [0x7ff71e7565d6]
-	(No symbol) [0x7ff71e7571b2]
-	(No symbol) [0x7ff71e763dc0]
-	(No symbol) [0x7ff71e7934f4]
-	(No symbol) [0x7ff71e789a8a]
-	(No symbol) [0x7ff71e7925d1]
-	(No symbol) [0x7ff71e777cb9]
-	(No symbol) [0x7ff71e778ff3]
-	(No symbol) [0x7ff71ee9e1a1]
-	(No symbol) [0x7ff71eec181b]
-	(No symbol) [0x7ff71eeb7ece]
-	(No symbol) [0x7ff71eb0b10e]
-	(No symbol) [0x7ff71e8f3db5]
-	(No symbol) [0x7ff71e8ee694]
-	(No symbol) [0x7ff71e8ee824]
-	(No symbol) [0x7ff71e8d6bdc]
-	(No symbol) [0x7ffa76dbdda7]
-	(No symbol) [0x7ffa784bee4c]
+	(No symbol) [0x7ff702a42e35]
+	(No symbol) [0x7ff702951dc0]
+	(No symbol) [0x7ff702d34fb1]
+	(No symbol) [0x7ff702fab158]
+	(No symbol) [0x7ff7027c6686]
+	(No symbol) [0x7ff7027c7262]
+	(No symbol) [0x7ff7027d3e80]
+	(No symbol) [0x7ff702807194]
+	(No symbol) [0x7ff7027fdc6a]
+	(No symbol) [0x7ff702806271]
+	(No symbol) [0x7ff7027ebae9]
+	(No symbol) [0x7ff7027ece13]
+	(No symbol) [0x7ff702ed63c1]
+	(No symbol) [0x7ff702ef987b]
+	(No symbol) [0x7ff702eee240]
+	(No symbol) [0x7ff702b6b4ee]
+	(No symbol) [0x7ff702960985]
+	(No symbol) [0x7ff70295b9e4]
+	(No symbol) [0x7ff70295bb74]
+	(No symbol) [0x7ff702944bfc]
+	(No symbol) [0x7ff944fedda7]
+	(No symbol) [0x7ff945c5ee4c]
 </t>
         </is>
       </c>
